--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC プロファイル検証ツール</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC プロファイル検証ツール · IccProfLib 採用</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>エラー:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>XML に変換</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>JSON に変換</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ICC に変換</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>XML に変換中…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>JSON に変換中…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ICC に変換中…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ICC プロファイルを読み込み</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>プロファイル ID</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>インデント</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>キーをソート</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>検証出力なし</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>有効</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>警告</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>エラー</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>不明</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>コンテキストで表示</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>検証の詳細</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>トリガー項目</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>現在の値</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>必須: 0</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>期待値: {value}</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>無効</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>閉じる</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>キーをソート</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>有効</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>警告</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>エラー</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>不明</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>コンテキストで表示</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>検証の詳細</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>トリガー項目</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>項目</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>現在の値</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>必須: 0</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>期待値: {value}</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>無効</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>閉じる</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>インデント</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>キーをソート</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>生出力</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>エラー:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>XML に変換</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>JSON に変換</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>ICC に変換</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>XML に変換中…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>JSON に変換中…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>ICC に変換中…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>プロファイル ID</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>タグ名</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>オフセット</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>サイズ</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>パディング</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>型</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>{type} の配列</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>（内容なし）</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>バイト</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>検証出力なし</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>プロファイルは有効です</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>型</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>重大な検証エラー</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>不明な検証ステータス</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>有効</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>警告</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>エラー</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>不明</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>コンテキストで表示</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>検証の詳細</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>トリガー項目</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>項目</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>現在の値</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>必須: 0</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>期待値: {value}</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>無効</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>閉じる</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>インデント</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>キーをソート</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>エラー:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>XML に変換</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>JSON に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>ICC に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>XML に変換中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>JSON に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>ICC に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>タグ名</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>オフセット</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>サイズ</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>パディング</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>型</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>{type} の配列</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>（内容なし）</v>
+        <v>型</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>バイト</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>検証出力なし</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>プロファイルは有効です</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>不明な検証ステータス</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>有効</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>警告</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>エラー</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>不明</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>コンテキストで表示</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>検証の詳細</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>トリガー項目</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>現在の値</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>必須: 0</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>期待値: {value}</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>無効</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>閉じる</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>キーをソート</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,695 +517,927 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
-        <v>リファレンス実装で検証します。</v>
+        <v>デモ実装で検証します。</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>検証中…</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>または</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>ファイルを選択</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>または</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>ヘッダー</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>タグ</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>検証</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>タグ</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>生出力</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>色度</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>散布図</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>エラー:</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>XML に変換</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>JSON に変換</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>ICC に変換</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>XML に変換中…</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>JSON に変換中…</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC に変換中…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>プロファイル ID</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>タグが見つかりません。</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>タグ名</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>オフセット</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>サイズ</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>パディング</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>型</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>{type} の配列</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>（内容なし）</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>バイト</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>検証出力なし</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>プロファイルは有効です</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>重大な検証エラー</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>不明な検証ステータス</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>有効</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>警告</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>エラー</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>不明</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>コンテキストで表示</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>検証の詳細</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>トリガー項目</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>項目</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>現在の値</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>必須: 0</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>期待値: {value}</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>無効</v>
+        <v>型</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>閉じる</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>インデント</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>キーをソート</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>適合性</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>品質</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>レポート</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>不合格</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>エラー:</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>XML に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>JSON に変換</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>ICC に変換</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>XML に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>JSON に変換中…</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC に変換中…</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>プロファイル ID</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>タグが見つかりません。</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>タグ名</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>オフセット</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>サイズ</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>パディング</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>型</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>型</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>{type} の配列</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>（内容なし）</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>バイト</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>検証出力なし</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>プロファイルは有効です</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>重大な検証エラー</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>有効</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>警告</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>エラー</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>不明</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>合格</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>不合格</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>コンテキストで表示</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>検証の詳細</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>トリガー項目</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>項目</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>現在の値</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>必須: 0</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>期待値: {value}</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>無効</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>閉じる</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>インデント</v>
+        <v>キーをソート</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>キーをソート</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>ヘルプ</v>
+        <v>数値形式</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>お問い合わせ</v>
+        <v>16 進数</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>10 進数</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>ICC プロファイルをアップロードし、</v>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>仕様を</v>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>デモ実装で検証します。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>ICC プロファイルをアップロードし、</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>仕様を</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>検証中…</v>
+        <v>デモ実装で検証します。</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>または</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>ファイルを選択</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>ヘッダー</v>
+        <v>または</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>タグ</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>検証</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>プロット</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>生出力</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>カーブ</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>入力カーブ</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>出力カーブ</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>CLUT 画像</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>色域画像</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>色度</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>散布図</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>カーブ表</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>テーブル</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>データ</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>評価</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>読み込み中…</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>入力</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>出力</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>浮動小数点</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>グリッド点</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>正規化</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>人間可読</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>デバイス → PCS</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → デバイス</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>読み込み中…</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>適合性</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>品質</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>レポート</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>不合格</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>件のチェック</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>エラー:</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>XML に変換</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>JSON に変換</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>XML に変換中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>JSON に変換中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>ICC に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>タグ名</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>オフセット</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>サイズ</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>パディング</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>型</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>{type} の配列</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>（内容なし）</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>バイト</v>
+        <v>型</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>検証出力なし</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>プロファイルは有効です</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>不明な検証ステータス</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>有効</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>警告</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>エラー</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>不明</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>合格</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>不合格</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>コンテキストで表示</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>検証の詳細</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>トリガー項目</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>項目</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>現在の値</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>必須: 0</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>期待値: {value}</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>無効</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>閉じる</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>インデント</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>キーをソート</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>適合性</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>品質</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>レポート</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>エラー:</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>プロット</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>生出力</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>カーブ</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>入力カーブ</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>出力カーブ</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>CLUT 画像</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>色域画像</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>色度</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>散布図</v>
+        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>さらに表示（{n}）</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>カーブ表</v>
+        <v>すべて</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>テーブル</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>データ</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>評価</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>読み込み中…</v>
+        <v>L* トーン反転</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>入力</v>
+        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>出力</v>
+        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>浮動小数点</v>
+        <v>LUT テーブル</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>グリッド点</v>
+        <v>ΔL* しきい値 (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>正規化</v>
+        <v>ε = {eps} を超える反転：{n}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>人間可読</v>
+        <v>ε = {eps} を超える L* 反転はありません</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>デバイス → PCS</v>
+        <v>チャンネル</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → デバイス</v>
+        <v>インク（低 → 高）</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>読み込み中…</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>セキュリティ</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>適合性</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>品質</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>レポート</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>不合格</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>件のチェック</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>エラー:</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>XML に変換</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>JSON に変換</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC に変換</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>XML に変換中…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON に変換中…</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>ICC に変換中…</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>プロファイル ID</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>タグ名</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>オフセット</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>サイズ</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>パディング</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>型</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>{type} の配列</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>（内容なし）</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>バイト</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>検証出力なし</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>プロファイルは有効です</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>重大な検証エラー</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>不明な検証ステータス</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>有効</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>警告</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>エラー</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>不明</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>合格</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>不合格</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>コンテキストで表示</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>検証の詳細</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>トリガー項目</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>項目</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>現在の値</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>必須: 0</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>期待値: {value}</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>無効</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>閉じる</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>インデント</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>キーをソート</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ユーザーガイド</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>ICC プロファイルをアップロードし、</v>
+        <v>ガイドを検索</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>仕様を</v>
+        <v>ユーザーガイドを検索</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>デモ実装で検証します。</v>
+        <v>前の一致</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>次の一致</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>ユーザーガイドを閉じる</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>検証中…</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>ユーザーガイドを読み込めませんでした。</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>または</v>
+        <v>ICC プロファイルをアップロードし、</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>ファイルを選択</v>
+        <v>仕様を</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>デモ実装で検証します。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>ヘッダー</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>タグ</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>検証</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>分析</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>中立軸インキング</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>または</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>レンダリングインテント</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% インキ</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>知覚的</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>相対比色</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>彩度</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>さらに表示（{n}）</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>すべて</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>分析中…</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>分析</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>L* トーン反転</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>LUT テーブル</v>
+        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>ΔL* しきい値 (ε)</v>
+        <v>さらに表示（{n}）</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>ε = {eps} を超える反転：{n}</v>
+        <v>すべて</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>ε = {eps} を超える L* 反転はありません</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>チャンネル</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>インク（低 → 高）</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>プロット</v>
+        <v>L* トーン反転</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>生出力</v>
+        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>LUT テーブル</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>カーブ</v>
+        <v>ΔL* しきい値 (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>入力カーブ</v>
+        <v>ε = {eps} を超える反転：{n}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>出力カーブ</v>
+        <v>ε = {eps} を超える L* 反転はありません</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>CLUT 画像</v>
+        <v>チャンネル</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>色域画像</v>
+        <v>インク（低 → 高）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>色度</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>散布図</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>カーブ表</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>テーブル</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>データ</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>評価</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>読み込み中…</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>入力</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>出力</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>浮動小数点</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>グリッド点</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>正規化</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>人間可読</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>デバイス → PCS</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → デバイス</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>読み込み中…</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>セキュリティ</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>適合性</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>品質</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>レポート</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>不合格</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>件のチェック</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>{lib} 採用</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>通知を受け取る</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>閉じる</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>メールアドレス</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>you@example.com</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>（任意）</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>キャンセル</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>登録</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>閉じる</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>エラー:</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>XML に変換</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>JSON に変換</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>ICC に変換</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>XML に変換中…</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>JSON に変換中…</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>ICC に変換中…</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>プロファイル ID</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>タグが見つかりません。</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>タグ名</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>オフセット</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>サイズ</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>パディング</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>型</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>{type} の配列</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>（内容なし）</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>バイト</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>検証出力なし</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>プロファイルは有効です</v>
+        <v>型</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>重大な検証エラー</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>不明な検証ステータス</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>有効</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>警告</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>エラー</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>不明</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>合格</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>不合格</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>コンテキストで表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>検証の詳細</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>トリガー項目</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>項目</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>現在の値</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>必須: 0</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>期待値: {value}</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>無効</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>閉じる</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>インデント</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>キーをソート</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>さらに表示（{n}）</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>すべて</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>分析中…</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>分析</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>L* トーン反転</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>LUT テーブル</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>ΔL* しきい値 (ε)</v>
+        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>ε = {eps} を超える反転：{n}</v>
+        <v>さらに表示（{n}）</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>ε = {eps} を超える L* 反転はありません</v>
+        <v>すべて</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>チャンネル</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>インク（低 → 高）</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>プロット</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>生出力</v>
+        <v>L* トーン反転</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>カーブ</v>
+        <v>LUT テーブル</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>入力カーブ</v>
+        <v>ΔL* しきい値 (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>出力カーブ</v>
+        <v>ε = {eps} を超える反転：{n}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>CLUT 画像</v>
+        <v>ε = {eps} を超える L* 反転はありません</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>色域画像</v>
+        <v>チャンネル</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>色度</v>
+        <v>インク（低 → 高）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>散布図</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>カーブ表</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>テーブル</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>データ</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>評価</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>読み込み中…</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>入力</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>出力</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>浮動小数点</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>グリッド点</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>正規化</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>人間可読</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>デバイス → PCS</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → デバイス</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>セキュリティ</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>適合性</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>品質</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>レポート</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>不合格</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>件のチェック</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>{lib} 採用</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>通知を受け取る</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>閉じる</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>メールアドレス</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>you@example.com</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>（任意）</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>キャンセル</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>登録</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>閉じる</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>エラー:</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>XML に変換</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>JSON に変換</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>ICC に変換</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>XML に変換中…</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>JSON に変換中…</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC に変換中…</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>プロファイル ID</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>タグが見つかりません。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>タグ名</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>オフセット</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>サイズ</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>パディング</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>型</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>{type} の配列</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>（内容なし）</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>バイト</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>検証出力なし</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>プロファイルは有効です</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>型</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>重大な検証エラー</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>不明な検証ステータス</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>有効</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>警告</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>エラー</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>不明</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>合格</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>不合格</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>コンテキストで表示</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>検証の詳細</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>トリガー項目</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>項目</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>現在の値</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>必須: 0</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>期待値: {value}</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>無効</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>閉じる</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>インデント</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>キーをソート</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>反転の多いチャンネルは ΔL* が大きい上位 {shown} 件のみ表示します。</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>さらに表示（{n}）</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>すべて</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>分析中…</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>分析</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>L* トーン反転</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>インクを増やして色が明るくなることはないはずです。各デバイスチャンネルを走査し他を固定して、L* が上昇する箇所を検出します。アルゴリズムは元々 Harold Boll によるものです。</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>このプロファイルにはデバイス→PCS の CLUT がないため、L* 反転スキャンは適用されません（例：マトリックス/TRC ディスプレイプロファイル）。</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>LUT テーブル</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>ΔL* しきい値 (ε)</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>ε = {eps} を超える反転：{n}</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>ε = {eps} を超える L* 反転はありません</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>チャンネル</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>インク（低 → 高）</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>プロット</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>生出力</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>カーブ</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>入力カーブ</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>出力カーブ</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>CLUT 画像</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>色域画像</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>色度</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>散布図</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>カーブ表</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>テーブル</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>データ</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>評価</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>読み込み中…</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>入力</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>出力</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>浮動小数点</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>グリッド点</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>正規化</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>人間可読</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>デバイス → PCS</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → デバイス</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>読み込み中…</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>セキュリティ</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>適合性</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>品質</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>レポート</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>不合格</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>件のチェック</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>{lib} 採用</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="119">
@@ -1352,23 +1352,23 @@
         <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>通知を受け取る</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>メールアドレス</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>you@example.com</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>（任意）</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>キャンセル</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>登録</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>閉じる</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>エラー:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>XML に変換</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>JSON に変換</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>ICC に変換</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>XML に変換中…</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>JSON に変換中…</v>
+        <v>型</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>ICC に変換中…</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>プロファイル ID</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>タグが見つかりません。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>タグ名</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>オフセット</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>サイズ</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>パディング</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>型</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>{type} の配列</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>（内容なし）</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>バイト</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>検証出力なし</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>プロファイルは有効です</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>重大な検証エラー</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>不明な検証ステータス</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>有効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>警告</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>エラー</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>不明</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>合格</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>不合格</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>コンテキストで表示</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>検証の詳細</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>トリガー項目</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>項目</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>現在の値</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>必須: 0</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>期待値: {value}</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>無効</v>
+        <v>キーをソート</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>閉じる</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>XML エディタを読み込み中…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>JSON エディタを読み込み中…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● 未保存の XML 編集</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● 未保存の JSON 編集</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>インデント</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>キーをソート</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>平均</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>分析中…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>分析</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>プロット</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>生出力</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>カーブ</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>入力カーブ</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>出力カーブ</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>CLUT 画像</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>色域画像</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>色度</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>散布図</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>カーブ表</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>テーブル</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>データ</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>評価</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>読み込み中…</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>入力</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>出力</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>浮動小数点</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>グリッド点</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>正規化</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>人間可読</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>デバイス → PCS</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → デバイス</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>読み込み中…</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>適合性</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>品質</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>レポート</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>設定</v>
+        <v>ラウンドトリップ (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>表示</v>
+        <v>参照ツール iccRoundTrip と同様に、プロファイルのデバイスキューブでラウンドトリップを計算します。ラウンドトリップ 1 はデバイス→PCS→デバイスの誤差 (ΔE*ab)、ラウンドトリップ 2 は PCS ラウンドトリップの安定性です。PRMG ヒストグラムは Perceptual Reference Medium Gamut に対する相互運用性を示します。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>背景</v>
+        <v>MPE（カラー）タグを使用</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>言語</v>
+        <v>このプロファイルはラウンドトリップできません。この指標に必要なデバイス↔PCS 変換がありません（例：一方向または抽象プロファイル）。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>システム</v>
+        <v>ラウンドトリップをスキップしました：デバイスの色空間が広すぎて評価できません（サンプルが多すぎます）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>ライト</v>
+        <v>指標</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>ダーク</v>
+        <v>ラウンドトリップ 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>システム既定</v>
+        <v>ラウンドトリップ 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>数値形式</v>
+        <v>デバイス → PCS → デバイス</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>16 進数</v>
+        <v>PCS ラウンドトリップの安定性</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>10 進数</v>
+        <v>最小 ΔE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>ヘルプ</v>
+        <v>平均 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>お問い合わせ</v>
+        <v>最大 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>ユーザーガイド</v>
+        <v>最悪 L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>ガイドを検索</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>ユーザーガイドを検索</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>前の一致</v>
+        <v>指定なし</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>次の一致</v>
+        <v>未評価</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>ユーザーガイドを閉じる</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>読み込み中…</v>
+        <v>ラウンドトリップ ΔE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>ユーザーガイドを読み込めませんでした。</v>
+        <v>件数</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>なし</v>
+        <v>割合</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>合計</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>ICC プロファイルをアップロードし、</v>
+        <v>PRMG は未評価</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>仕様を</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>デモ実装で検証します。</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>背景</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>言語</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>検証中…</v>
+        <v>システム</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>ライト</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>ダーク</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>システム既定</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>または</v>
+        <v>数値形式</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>ファイルを選択</v>
+        <v>16 進数</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>10 進数</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>ヘッダー</v>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>タグ</v>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>検証</v>
+        <v>ユーザーガイド</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>分析</v>
+        <v>ガイドを検索</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>中立軸インキング</v>
+        <v>ユーザーガイドを検索</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>前の一致</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>次の一致</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>ユーザーガイドを閉じる</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>レンダリングインテント</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% インキ</v>
+        <v>ユーザーガイドを読み込めませんでした。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>知覚的</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>相対比色</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>彩度</v>
+        <v>ICC プロファイルをアップロードし、</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>絶対比色</v>
+        <v>仕様を</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>プロファイル統計</v>
+        <v>デモ実装で検証します。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>レンダリングインテント</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>往復 ΔE</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>平均</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>最大</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>分析中…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>分析</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>プロット</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>生出力</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>カーブ</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>入力カーブ</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>出力カーブ</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>CLUT 画像</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>色域画像</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>色度</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>散布図</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>カーブ表</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>テーブル</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>データ</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>評価</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>読み込み中…</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>入力</v>
+        <v>または</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>出力</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>浮動小数点</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>グリッド点</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>正規化</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>人間可読</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>デバイス → PCS</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → デバイス</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>読み込み中…</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>セキュリティ</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>適合性</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>品質</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>レポート</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>不合格</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>件のチェック</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>{lib} 採用</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>通知を受け取る</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>閉じる</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>メールアドレス</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>（任意）</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>キャンセル</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>登録</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>閉じる</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>エラー:</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>XML に変換</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>JSON に変換</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>ICC に変換</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>XML に変換中…</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>JSON に変換中…</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>ICC に変換中…</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>プロファイル ID</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>タグ名</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>オフセット</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>サイズ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>パディング</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>型</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>{type} の配列</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>（内容なし）</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>バイト</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>検証出力なし</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>プロファイルは有効です</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>重大な検証エラー</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>不明な検証ステータス</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>有効</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>警告</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>エラー</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>不明</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>合格</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>不合格</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>コンテキストで表示</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>検証の詳細</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>トリガー項目</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>項目</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>現在の値</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>必須: 0</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>期待値: {value}</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>無効</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>閉じる</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>インデント</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>キーをソート</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>設定</v>
+        <v>1 つのレンダリングインテントに対するプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積 (ΔE*ab³) と、ラウンドトリップ精度の指標。レンダリングインテントとラウンドトリップの種類を選ぶと、表とヒストグラムがそれに合わせて更新されます。</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>表示</v>
+        <v>ラウンドトリップの種類</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>背景</v>
+        <v>このラウンドトリップの種類には影響しません</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>言語</v>
+        <v>このラウンドトリップの種類はこのプロファイルでは利用できません。</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>システム</v>
+        <v>ラウンドトリップ ΔE 分布</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>ライト</v>
+        <v>評価領域内に該当するラウンドトリップのサンプルはありませんでした。</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>ダーク</v>
+        <v>標準偏差</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>システム既定</v>
+        <v>相対度数</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>数値形式</v>
+        <v>累積度数</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>16 進数</v>
+        <v>水平スケール</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>10 進数</v>
+        <v>整数 ΔE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>ヘルプ</v>
+        <v>自動スケール</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>お問い合わせ</v>
+        <v>ビン</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>ユーザーガイド</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>ガイドを検索</v>
+        <v>デバイス↔PCS 変換のカラールックアップテーブル (CLUT) を 1 枚の画像にタイル状に並べたものです。表示するレンダリングインテントのテーブルを選んでください。</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>ユーザーガイドを検索</v>
+        <v>このプロファイルには可視化できる CLUT ベースのデバイス↔PCS テーブルがありません。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>前の一致</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>次の一致</v>
+        <v>色域タグの色域内/外マップ：PCS 色が再現できる箇所はニュートラル、デバイス色域の外に出る箇所は赤で示されます。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>ユーザーガイドを閉じる</v>
+        <v>このプロファイルには可視化できる色域タグがありません。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>読み込み中…</v>
+        <v>垂直スケール</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>ユーザーガイドを読み込めませんでした。</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>なし</v>
+        <v>トーン増加</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>トーン増加（出力 − 入力）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC プロファイルをアップロードし、</v>
+        <v>完全なダンプを表示</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>仕様を</v>
+        <v>パフォーマンスのため出力を切り詰めました。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>デモ実装で検証します。</v>
+        <v>色域内の概要 (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>反転 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>再現性 (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>検証中…</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>iccviz の概要：デバイス値のグリッドを PCS へ、デバイスへ戻し、再び PCS へと変換し、2 回の PCS 結果の間で ΔE*ab を測定します。色域内の安定性を素早く確認します。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>iccRoundTrip ラウンドトリップ 1：各デバイス色の PCS と、Lab → デバイス → Lab を 1 回ラウンドトリップした後の PCS との間の ΔE*ab。反転精度と色域マッピングを反映します。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip ラウンドトリップ 2：1 回目と 2 回目のラウンドトリップの間の ΔE*ab — 繰り返す PCS ラウンドトリップの安定性（再現性。1 回目の色域クリッピングとは無関係）を示します。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内の PCS 色を 1 回ラウンドトリップ（Lab → デバイス → Lab）します。ΔE*ab 分布はプロファイル間の相互運用性を示します。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>設定</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>表示</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>背景</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>言語</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>システム</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>ライト</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>ダーク</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>システム既定</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>数値形式</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>16 進数</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>10 進数</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>ユーザーガイド</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>ガイドを検索</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>ユーザーガイドを検索</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>前の一致</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>次の一致</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>ユーザーガイドを閉じる</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>ユーザーガイドを読み込めませんでした。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>または</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>ファイルを選択</v>
+        <v>ICC プロファイルをアップロードし、</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>仕様を</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>ヘッダー</v>
+        <v>デモ実装で検証します。</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>タグ</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>検証</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>分析</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>中立軸インキング</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>プロファイルプールを表示</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>レンダリングインテント</v>
+        <v>折りたたむ</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% インキ</v>
+        <v>プロファイルを読み込む</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>知覚的</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>相対比色</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>彩度</v>
+        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>絶対比色</v>
+        <v>.cube から新規作成</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>プロファイル統計</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>.cube から新しいプロファイル</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>レンダリングインテント</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>.cube ファイルを選択</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>往復 ΔE</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>またはここにドロップするか、下に貼り付けてください</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>平均</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>DeviceLink を作成</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>最大</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>分析中…</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>分析</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>プロット</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>生出力</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>カーブ</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>入力カーブ</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>出力カーブ</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>CLUT 画像</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>色域画像</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>色度</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>散布図</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>カーブ表</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>テーブル</v>
+        <v>色</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>データ</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>評価</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>読み込み中…</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>入力</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>出力</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>浮動小数点</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>グリッド点</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>正規化</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>人間可読</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>デバイス → PCS</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → デバイス</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>読み込み中…</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>セキュリティ</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>適合性</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>品質</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>レポート</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>不合格</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>件のチェック</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>{lib} 採用</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>通知を受け取る</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>閉じる</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>メールアドレス</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>you@example.com</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>（任意）</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>または</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>キャンセル</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>登録</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>閉じる</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>エラー:</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>XML に変換</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>JSON に変換</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>ICC に変換</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>XML に変換中…</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>JSON に変換中…</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>ICC に変換中…</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>プロファイル ID</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>タグが見つかりません。</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>タグ名</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>オフセット</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>サイズ</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>パディング</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>型</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>{type} の配列</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>（内容なし）</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>バイト</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>検証出力なし</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>プロファイルは有効です</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>重大な検証エラー</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>不明な検証ステータス</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>有効</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>警告</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>エラー</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>不明</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>合格</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>不合格</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>コンテキストで表示</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>検証の詳細</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>トリガー項目</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>項目</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>現在の値</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>必須: 0</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>期待値: {value}</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>無効</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>閉じる</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>インデント</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>キーをソート</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC プロファイルツール</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>{lib} 採用</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>通知を受け取る</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>profiletool の新リリース通知を受け取る</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>新しいリリースの通知を受け取る</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>メールアドレス</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>profiletool をどのように使いますか？</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>（任意）</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>例：印刷校正のためのICCプロファイル評価</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>キャンセル</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>登録</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>ありがとうございます — ご連絡します。</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>プライバシーに関する通知</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>有効なメールアドレスを入力してください。</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>フォームを確認してもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>ネットワークエラーです。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>エラー:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>XML に変換</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>JSON に変換</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>ICC に変換</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>XML に変換中…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>JSON に変換中…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>ICC に変換中…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>ICC プロファイルを読み込み</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>プロファイル ID</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>リンク</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>削除</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>色域比較</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>レンダリングインテント</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>シェル</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>不透明度</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>色</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>単色</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>値による</v>
+        <v>色</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>色相による</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>回転</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>ターンテーブル</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>オービット</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>ドラッグ速度</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>ロール</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>ロール速度</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>色域を構築中…</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>色域なし</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>表示/非表示</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 色域シェル</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 色域スライス</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>平面</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>リンク</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>プロファイル名</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>作成</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>作成中…</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>キャンセル</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>または</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>ファイルを選択</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>ヘッダー</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>タグ</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>検証</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>分析</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>中立軸インキング</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>レンダリングインテント</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% インキ</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>知覚的</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>相対比色</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>彩度</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>絶対比色</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>プロファイル統計</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>レンダリングインテント</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>往復 ΔE</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>平均</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>最大</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>分析中…</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>分析</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>プロット</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>生出力</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>カーブ</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>入力カーブ</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>出力カーブ</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>CLUT 画像</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>色域画像</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>色度</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>散布図</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>カーブ表</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>テーブル</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>データ</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>評価</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>読み込み中…</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>入力</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>出力</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>浮動小数点</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>グリッド点</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>正規化</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>人間可読</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>デバイス → PCS</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → デバイス</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>読み込み中…</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>セキュリティ</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>適合性</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>品質</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>レポート</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>不合格</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>件のチェック</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>{lib} 採用</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>通知を受け取る</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>閉じる</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>メールアドレス</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>you@example.com</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>（任意）</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>キャンセル</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>登録</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>閉じる</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>または</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>エラー:</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>XML に変換</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>JSON に変換</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>ICC に変換</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>XML に変換中…</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>JSON に変換中…</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>ICC に変換中…</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>プロファイル ID</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>タグが見つかりません。</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>タグ名</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>オフセット</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>サイズ</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>パディング</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>型</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>{type} の配列</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>（内容なし）</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>バイト</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>検証出力なし</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>プロファイルは有効です</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>重大な検証エラー</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>不明な検証ステータス</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>有効</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>警告</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>エラー</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>不明</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>合格</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>不合格</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>コンテキストで表示</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>検証の詳細</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>トリガー項目</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>項目</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>現在の値</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>必須: 0</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>期待値: {value}</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>無効</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>閉じる</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>インデント</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>キーをソート</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Profile Assessment WG レポートを読み込み中…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Profile Assessment WG チェックを実行中…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Profile Assessment WG レポート</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>セキュリティ</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>適合性</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>品質</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>レポート</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>件のチェック</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ICC プロファイルツール</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>{lib} 採用</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>通知を受け取る</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>profiletool の新リリース通知を受け取る</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>新しいリリースの通知を受け取る</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>メールアドレス</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>profiletool をどのように使いますか？</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>（任意）</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>例：印刷校正のためのICCプロファイル評価</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>キャンセル</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>登録</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>ありがとうございます — ご連絡します。</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>プライバシーに関する通知</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>有効なメールアドレスを入力してください。</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>フォームを確認してもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>ネットワークエラーです。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>エラー:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>XML に変換</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>JSON に変換</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>ICC に変換</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>XML に変換中…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>JSON に変換中…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>ICC に変換中…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>ICC プロファイルを読み込み</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>プロファイル ID</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC プロファイルをアップロードし、</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>仕様を</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>デモ実装で検証します。</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>検証中…</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>プロファイルプールを表示</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>折りたたむ</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>プロファイル</v>
+        <v>プロファイルを読み込む</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>プロファイルプールを表示</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>折りたたむ</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>プロファイルを読み込む</v>
+        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>削除</v>
+        <v>.cube から新規作成</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>.cube から新規作成</v>
+        <v>.cube から新しいプロファイル</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>名前で並べ替え</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>.cube ファイルを選択</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>.cube から新しいプロファイル</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>.cube ファイルを選択</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>またはここにドロップするか、下に貼り付けてください</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>キャンセル</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>DeviceLink を作成</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>作成中…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>キャンセル</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>DeviceLink を作成</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>作成中…</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>プロファイル</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>比較</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>リンク</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>スペクトル</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>削除</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>色域比較</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>レンダリングインテント</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>シェル</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>色</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>軸の数値</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>不透明度</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>色</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>単色</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>値による</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>色相による</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>回転</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>ターンテーブル</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>オービット</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>ドラッグ速度</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>ロール</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>ロール速度</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>色域を構築中…</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>色域なし</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>表示/非表示</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>3D 色域シェル</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>2D 色域スライス</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>平面</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>リンク</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>プロファイル名</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>作成</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>作成中…</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>リンクパイプライン</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>完了</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>画像を確認中…</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>画像を変換</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>変換中…</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>削除済み</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>前に移動</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>後に移動</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>上に移動</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>下に移動</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>レンダリングインテント（すべて）</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>この変換のレンダリングインテント</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>チェーン</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>チェーンを解析できませんでした。</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>チェーンを確認中…</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>チェーンが接続していません（{detail}）。</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>画像を処理する前にチェーンを修正してください</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>クリア</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>DeviceLinkを作成</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>DeviceLink名</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>作成中…</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>画像を処理するにはチェーンを作成してください</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>変換した画像を保存しました。</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>データファイルが大きすぎます。</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>データを変換</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>変換中…</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>優先</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>観測者</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>光源</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>条件</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>重複を{n}件フィルタ</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>中央値</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>平均値</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>パッチ</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>重複{n}件</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>変換結果</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} ・ {n}パッチ</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>名前を付けて保存</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>保存</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>変換を反転</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>反転中…</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>反転</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>最後の段階</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>最初の段階</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>{in}のデータ → {out}を検索</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>ΔEコスト</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>この画像には埋め込みICCプロファイルがあります。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>抽出してチェーンに追加</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>抽出中…</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>閉じる</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>画像出力オプション</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>エンコーディング</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>元と同じ</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8ビット</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16ビット</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>浮動小数点（32ビット）</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>圧縮</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>なし</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>プレーナー</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>コンポジット</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>セパレート</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>CMM補間</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>四面体</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>線形</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>ICCを埋め込む</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>スペクトルTIFFを組み立て</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>ch</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>組み立てて保存</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>組み立て中…</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>{n}チャンネルを組み立てました。</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>キャンセル</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>または</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>または</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>ファイルを選択</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>ヘッダー</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>タグ</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>検証</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>分析</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>中立軸インキング</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>レンダリングインテント</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% インキ</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>知覚的</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>相対比色</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>彩度</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>絶対比色</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>プロファイル統計</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>レンダリングインテント</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>往復 ΔE</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>平均</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>最大</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>分析中…</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>分析</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>プロット</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>生出力</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>カーブ</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>入力カーブ</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>出力カーブ</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>CLUT 画像</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>色域画像</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>色度</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>散布図</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>カーブ表</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>テーブル</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>データ</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>評価</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>読み込み中…</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>入力</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>出力</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>浮動小数点</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>グリッド点</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>正規化</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>人間可読</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>デバイス → PCS</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → デバイス</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>読み込み中…</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>セキュリティ</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>適合性</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>品質</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>レポート</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>不合格</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>件のチェック</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>{lib} 採用</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>通知を受け取る</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>閉じる</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>メールアドレス</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>you@example.com</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>（任意）</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>キャンセル</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>登録</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>閉じる</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>エラー:</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>XML に変換</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>JSON に変換</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>ICC に変換</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>JSON に変換中…</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>ICC に変換中…</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>プロファイル ID</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>タグが見つかりません。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>タグ名</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>オフセット</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>サイズ</v>
+        <v>型</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>パディング</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>型</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>{type} の配列</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>（内容なし）</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>バイト</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>検証出力なし</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>プロファイルは有効です</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>重大な検証エラー</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>不明な検証ステータス</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>有効</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>警告</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>エラー</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>不明</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>合格</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>不合格</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>コンテキストで表示</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>検証の詳細</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>トリガー項目</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>項目</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>現在の値</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>必須: 0</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>期待値: {value}</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>無効</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>閉じる</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>キーをソート</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>インデント</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>キーをソート</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>ラウンドトリップ (PRMG)</v>
+        <v>サンプルの {pct}% が範囲外のためクランプされました。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>参照ツール iccRoundTrip と同様に、プロファイルのデバイスキューブでラウンドトリップを計算します。ラウンドトリップ 1 はデバイス→PCS→デバイスの誤差 (ΔE*ab)、ラウンドトリップ 2 は PCS ラウンドトリップの安定性です。PRMG ヒストグラムは Perceptual Reference Medium Gamut に対する相互運用性を示します。</v>
+        <v>ラウンドトリップ (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>MPE（カラー）タグを使用</v>
+        <v>参照ツール iccRoundTrip と同様に、プロファイルのデバイスキューブでラウンドトリップを計算します。ラウンドトリップ 1 はデバイス→PCS→デバイスの誤差 (ΔE*ab)、ラウンドトリップ 2 は PCS ラウンドトリップの安定性です。PRMG ヒストグラムは Perceptual Reference Medium Gamut に対する相互運用性を示します。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>このプロファイルはラウンドトリップできません。この指標に必要なデバイス↔PCS 変換がありません（例：一方向または抽象プロファイル）。</v>
+        <v>MPE（カラー）タグを使用</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>ラウンドトリップをスキップしました：デバイスの色空間が広すぎて評価できません（サンプルが多すぎます）。</v>
+        <v>このプロファイルはラウンドトリップできません。この指標に必要なデバイス↔PCS 変換がありません（例：一方向または抽象プロファイル）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>指標</v>
+        <v>ラウンドトリップをスキップしました：デバイスの色空間が広すぎて評価できません（サンプルが多すぎます）。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>ラウンドトリップ 1</v>
+        <v>指標</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>ラウンドトリップ 2</v>
+        <v>ラウンドトリップ 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>デバイス → PCS → デバイス</v>
+        <v>ラウンドトリップ 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>PCS ラウンドトリップの安定性</v>
+        <v>デバイス → PCS → デバイス</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>最小 ΔE</v>
+        <v>PCS ラウンドトリップの安定性</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>平均 ΔE</v>
+        <v>最小 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>最大 ΔE</v>
+        <v>平均 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>最悪 L, a, b</v>
+        <v>最大 ΔE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>指定色域</v>
+        <v>最悪 L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>指定なし</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>未評価</v>
+        <v>指定なし</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>PRMG 相互運用性</v>
+        <v>未評価</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>ラウンドトリップ ΔE</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>件数</v>
+        <v>ラウンドトリップ ΔE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>割合</v>
+        <v>件数</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>合計</v>
+        <v>割合</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG は未評価</v>
+        <v>合計</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>1 つのレンダリングインテントに対するプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積 (ΔE*ab³) と、ラウンドトリップ精度の指標。レンダリングインテントとラウンドトリップの種類を選ぶと、表とヒストグラムがそれに合わせて更新されます。</v>
+        <v>PRMG は未評価</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>ラウンドトリップの種類</v>
+        <v>1 つのレンダリングインテントに対するプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積 (ΔE*ab³) と、ラウンドトリップ精度の指標。レンダリングインテントとラウンドトリップの種類を選ぶと、表とヒストグラムがそれに合わせて更新されます。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>このラウンドトリップの種類には影響しません</v>
+        <v>ラウンドトリップの種類</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>このラウンドトリップの種類はこのプロファイルでは利用できません。</v>
+        <v>このラウンドトリップの種類には影響しません</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>ラウンドトリップ ΔE 分布</v>
+        <v>このラウンドトリップの種類はこのプロファイルでは利用できません。</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>評価領域内に該当するラウンドトリップのサンプルはありませんでした。</v>
+        <v>ラウンドトリップ ΔE 分布</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>標準偏差</v>
+        <v>評価領域内に該当するラウンドトリップのサンプルはありませんでした。</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>相対度数</v>
+        <v>標準偏差</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>累積度数</v>
+        <v>相対度数</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>水平スケール</v>
+        <v>累積度数</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>整数 ΔE</v>
+        <v>水平スケール</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>自動スケール</v>
+        <v>整数 ΔE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>ビン</v>
+        <v>自動スケール</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>CLUT 画像</v>
+        <v>ビン</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>デバイス↔PCS 変換のカラールックアップテーブル (CLUT) を 1 枚の画像にタイル状に並べたものです。表示するレンダリングインテントのテーブルを選んでください。</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>このプロファイルには可視化できる CLUT ベースのデバイス↔PCS テーブルがありません。</v>
+        <v>デバイス↔PCS 変換のカラールックアップテーブル (CLUT) を 1 枚の画像にタイル状に並べたものです。表示するレンダリングインテントのテーブルを選んでください。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>色域画像</v>
+        <v>このプロファイルには可視化できる CLUT ベースのデバイス↔PCS テーブルがありません。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>色域タグの色域内/外マップ：PCS 色が再現できる箇所はニュートラル、デバイス色域の外に出る箇所は赤で示されます。</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>このプロファイルには可視化できる色域タグがありません。</v>
+        <v>色域タグの色域内/外マップ：PCS 色が再現できる箇所はニュートラル、デバイス色域の外に出る箇所は赤で示されます。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>垂直スケール</v>
+        <v>このプロファイルには可視化できる色域タグがありません。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>垂直スケール</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>トーン増加</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>トーン増加（出力 − 入力）</v>
+        <v>トーン増加</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>完全なダンプを表示</v>
+        <v>トーン増加（出力 − 入力）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>パフォーマンスのため出力を切り詰めました。</v>
+        <v>完全なダンプを表示</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>色域内の概要 (RT0)</v>
+        <v>パフォーマンスのため出力を切り詰めました。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>反転 + 色域 (RT1)</v>
+        <v>色域内の概要 (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>再現性 (RT2)</v>
+        <v>反転 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>PRMG 相互運用性</v>
+        <v>再現性 (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>iccviz の概要：デバイス値のグリッドを PCS へ、デバイスへ戻し、再び PCS へと変換し、2 回の PCS 結果の間で ΔE*ab を測定します。色域内の安定性を素早く確認します。</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip ラウンドトリップ 1：各デバイス色の PCS と、Lab → デバイス → Lab を 1 回ラウンドトリップした後の PCS との間の ΔE*ab。反転精度と色域マッピングを反映します。</v>
+        <v>iccviz の概要：デバイス値のグリッドを PCS へ、デバイスへ戻し、再び PCS へと変換し、2 回の PCS 結果の間で ΔE*ab を測定します。色域内の安定性を素早く確認します。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip ラウンドトリップ 2：1 回目と 2 回目のラウンドトリップの間の ΔE*ab — 繰り返す PCS ラウンドトリップの安定性（再現性。1 回目の色域クリッピングとは無関係）を示します。</v>
+        <v>iccRoundTrip ラウンドトリップ 1：各デバイス色の PCS と、Lab → デバイス → Lab を 1 回ラウンドトリップした後の PCS との間の ΔE*ab。反転精度と色域マッピングを反映します。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内の PCS 色を 1 回ラウンドトリップ（Lab → デバイス → Lab）します。ΔE*ab 分布はプロファイル間の相互運用性を示します。</v>
+        <v>iccRoundTrip ラウンドトリップ 2：1 回目と 2 回目のラウンドトリップの間の ΔE*ab — 繰り返す PCS ラウンドトリップの安定性（再現性。1 回目の色域クリッピングとは無関係）を示します。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>設定</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内の PCS 色を 1 回ラウンドトリップ（Lab → デバイス → Lab）します。ΔE*ab 分布はプロファイル間の相互運用性を示します。</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>表示</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>背景</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>言語</v>
+        <v>背景</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>システム</v>
+        <v>言語</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>ライト</v>
+        <v>システム</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>ダーク</v>
+        <v>ライト</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>システム既定</v>
+        <v>ダーク</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>数値形式</v>
+        <v>システム既定</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>16 進数</v>
+        <v>数値形式</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>10 進数</v>
+        <v>16 進数</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>ヘルプ</v>
+        <v>10 進数</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>お問い合わせ</v>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>ユーザーガイド</v>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>ガイドを検索</v>
+        <v>ユーザーガイド</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>ユーザーガイドを検索</v>
+        <v>ガイドを検索</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>前の一致</v>
+        <v>ユーザーガイドを検索</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>次の一致</v>
+        <v>前の一致</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>ユーザーガイドを閉じる</v>
+        <v>次の一致</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>読み込み中…</v>
+        <v>ユーザーガイドを閉じる</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>ユーザーガイドを読み込めませんでした。</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>なし</v>
+        <v>ユーザーガイドを読み込めませんでした。</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v>のデモ実装に基づく</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>検証中…</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>プロファイル</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>プロファイルプールを表示</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>折りたたむ</v>
+        <v>プロファイルプールを表示</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>プロファイルを読み込む</v>
+        <v>折りたたむ</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>削除</v>
+        <v>プロファイルを読み込む</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>.cube から新規作成</v>
+        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>名前で並べ替え</v>
+        <v>.cube から新規作成</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>.cube から新しいプロファイル</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
+        <v>.cube から新しいプロファイル</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>.cube ファイルを選択</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>.cube ファイルを選択</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>またはここにドロップするか、下に貼り付けてください</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>キャンセル</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>DeviceLink を作成</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink を作成</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>プロファイル</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>比較</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>リンク</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>スペクトル</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>削除</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>色域比較</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>レンダリングインテント</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>シェル</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>軸の数値</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>不透明度</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>色</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>単色</v>
+        <v>色</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>値による</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>色相による</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>回転</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>ターンテーブル</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>オービット</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>ドラッグ速度</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>ロール</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>ロール速度</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>色域を構築中…</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>色域なし</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>表示/非表示</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>3D 色域シェル</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>2D 色域スライス</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>平面</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>リンク</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>プロファイル名</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>作成</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>作成中…</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>リンクパイプライン</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>完了</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>画像を確認中…</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>画像を変換</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>変換中…</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>削除済み</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>前に移動</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>後に移動</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>上に移動</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>下に移動</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>レンダリングインテント（すべて）</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>この変換のレンダリングインテント</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>チェーン</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>チェーンを解析できませんでした。</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>チェーンを確認中…</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>チェーンが接続していません（{detail}）。</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>画像を処理する前にチェーンを修正してください</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>クリア</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>DeviceLinkを作成</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink名</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>画像を処理するにはチェーンを作成してください</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>変換した画像を保存しました。</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>データファイルが大きすぎます。</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>データを変換</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>変換中…</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>優先</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>観測者</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>光源</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>重複を{n}件フィルタ</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>中央値</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>平均値</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>パッチ</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>重複{n}件</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>変換結果</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} ・ {n}パッチ</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>名前を付けて保存</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>保存</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>変換を反転</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>反転中…</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>反転</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>最後の段階</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>最初の段階</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>{in}のデータ → {out}を検索</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>ΔEコスト</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>この画像には埋め込みICCプロファイルがあります。</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>抽出してチェーンに追加</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>抽出中…</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>閉じる</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>画像出力オプション</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>エンコーディング</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>元と同じ</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8ビット</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16ビット</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>浮動小数点（32ビット）</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>圧縮</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>なし</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>プレーナー</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>コンポジット</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>セパレート</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>CMM補間</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>四面体</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>線形</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>ICCを埋め込む</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>スペクトルTIFFを組み立て</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>ch</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>組み立てて保存</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>組み立て中…</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>{n}チャンネルを組み立てました。</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>キャンセル</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>または</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>ファイルを選択</v>
+        <v>または</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>ヘッダー</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>タグ</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>検証</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>分析</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>中立軸インキング</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% インキ</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>知覚的</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>相対比色</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>彩度</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>絶対比色</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>プロファイル統計</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>往復 ΔE</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>平均</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>分析中…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>分析</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>プロット</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>生出力</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>カーブ</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>入力カーブ</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>出力カーブ</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>CLUT 画像</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>色域画像</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>色度</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>散布図</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>カーブ表</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>テーブル</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>データ</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>評価</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>読み込み中…</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>入力</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>出力</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>浮動小数点</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>グリッド点</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>正規化</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>人間可読</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>デバイス → PCS</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → デバイス</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>読み込み中…</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>適合性</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>品質</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>レポート</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>知覚的</v>
+        <v>L* 出力（トーン）</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>相対比色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>彩度</v>
+        <v>極値の測色</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>絶対比色</v>
+        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>プロファイル統計</v>
+        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>相対</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>絶対</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>レンダリングインテント</v>
+        <v>白色点</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>黒色点</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>往復 ΔE</v>
+        <v>黒色点でのインキング</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>平均</v>
+        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>最大</v>
+        <v>ベタとクロマ最大点</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>分析中…</v>
+        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>分析</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>ベタ</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>プロット</v>
+        <v>C* 最大</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>生出力</v>
+        <v>そのインキング</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>シャドウ部のインキ使用量</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>カーブ</v>
+        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>入力カーブ</v>
+        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>出力カーブ</v>
+        <v>L* 一定の平面</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>CLUT 画像</v>
+        <v>黒色点補償の起点</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>色域画像</v>
+        <v>経路上の位置</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>色度</v>
+        <v>経路</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>散布図</v>
+        <v>シアン</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>マゼンタ</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>カーブ表</v>
+        <v>イエロー</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>テーブル</v>
+        <v>レッド</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>データ</v>
+        <v>グリーン</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>評価</v>
+        <v>ブルー</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>読み込み中…</v>
+        <v>ブラック</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>入力</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>出力</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>浮動小数点</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>グリッド点</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>正規化</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>人間可読</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>デバイス → PCS</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → デバイス</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>読み込み中…</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>セキュリティ</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>適合性</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>品質</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>レポート</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>不合格</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>件のチェック</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>{lib} 採用</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>通知を受け取る</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>閉じる</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>メールアドレス</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>you@example.com</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>（任意）</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>キャンセル</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>登録</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>閉じる</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>エラー:</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>XML に変換</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>JSON に変換</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>ICC に変換</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>XML に変換中…</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>JSON に変換中…</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>ICC に変換中…</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>タグ名</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>オフセット</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>サイズ</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>パディング</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>型</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>{type} の配列</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>（内容なし）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>バイト</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>検証出力なし</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>プロファイルは有効です</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>重大な検証エラー</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>不明な検証ステータス</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>有効</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>警告</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>エラー</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>不明</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>合格</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>不合格</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>コンテキストで表示</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>検証の詳細</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>トリガー項目</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>項目</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>現在の値</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>必須: 0</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>期待値: {value}</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>無効</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>閉じる</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>型</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>インデント</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>キーをソート</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>指定色域</v>
+        <v>明度別のラウンドトリップ ΔE</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L*（要求された色の明度）</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>指定なし</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>未評価</v>
+        <v>ポイント、色域境界 → ニュートラル</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>PRMG 相互運用性</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>ラウンドトリップ ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>件数</v>
+        <v>指定なし</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>割合</v>
+        <v>未評価</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>合計</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG は未評価</v>
+        <v>ラウンドトリップ ΔE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>1 つのレンダリングインテントに対するプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積 (ΔE*ab³) と、ラウンドトリップ精度の指標。レンダリングインテントとラウンドトリップの種類を選ぶと、表とヒストグラムがそれに合わせて更新されます。</v>
+        <v>件数</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>ラウンドトリップの種類</v>
+        <v>割合</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>このラウンドトリップの種類には影響しません</v>
+        <v>合計</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>このラウンドトリップの種類はこのプロファイルでは利用できません。</v>
+        <v>PRMG は未評価</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>ラウンドトリップ ΔE 分布</v>
+        <v>1 つのレンダリングインテントに対するプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積 (ΔE*ab³) と、ラウンドトリップ精度の指標。レンダリングインテントとラウンドトリップの種類を選ぶと、表とヒストグラムがそれに合わせて更新されます。</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>評価領域内に該当するラウンドトリップのサンプルはありませんでした。</v>
+        <v>ラウンドトリップの種類</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>標準偏差</v>
+        <v>このラウンドトリップの種類には影響しません</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>相対度数</v>
+        <v>このラウンドトリップの種類はこのプロファイルでは利用できません。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>累積度数</v>
+        <v>ラウンドトリップ ΔE 分布</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>水平スケール</v>
+        <v>評価領域内に該当するラウンドトリップのサンプルはありませんでした。</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>整数 ΔE</v>
+        <v>標準偏差</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>自動スケール</v>
+        <v>相対度数</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>ビン</v>
+        <v>累積度数</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>CLUT 画像</v>
+        <v>水平スケール</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>デバイス↔PCS 変換のカラールックアップテーブル (CLUT) を 1 枚の画像にタイル状に並べたものです。表示するレンダリングインテントのテーブルを選んでください。</v>
+        <v>整数 ΔE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>このプロファイルには可視化できる CLUT ベースのデバイス↔PCS テーブルがありません。</v>
+        <v>自動スケール</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>色域画像</v>
+        <v>ビン</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>色域タグの色域内/外マップ：PCS 色が再現できる箇所はニュートラル、デバイス色域の外に出る箇所は赤で示されます。</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>このプロファイルには可視化できる色域タグがありません。</v>
+        <v>デバイス↔PCS 変換のカラールックアップテーブル (CLUT) を 1 枚の画像にタイル状に並べたものです。表示するレンダリングインテントのテーブルを選んでください。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>垂直スケール</v>
+        <v>このプロファイルには可視化できる CLUT ベースのデバイス↔PCS テーブルがありません。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>トーン増加</v>
+        <v>色域タグの色域内/外マップ：PCS 色が再現できる箇所はニュートラル、デバイス色域の外に出る箇所は赤で示されます。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>トーン増加（出力 − 入力）</v>
+        <v>このプロファイルには可視化できる色域タグがありません。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>完全なダンプを表示</v>
+        <v>垂直スケール</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>パフォーマンスのため出力を切り詰めました。</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>色域内の概要 (RT0)</v>
+        <v>トーン増加</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>反転 + 色域 (RT1)</v>
+        <v>トーン増加（出力 − 入力）</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>再現性 (RT2)</v>
+        <v>完全なダンプを表示</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>PRMG 相互運用性</v>
+        <v>パフォーマンスのため出力を切り詰めました。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>iccviz の概要：デバイス値のグリッドを PCS へ、デバイスへ戻し、再び PCS へと変換し、2 回の PCS 結果の間で ΔE*ab を測定します。色域内の安定性を素早く確認します。</v>
+        <v>色域内の概要 (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip ラウンドトリップ 1：各デバイス色の PCS と、Lab → デバイス → Lab を 1 回ラウンドトリップした後の PCS との間の ΔE*ab。反転精度と色域マッピングを反映します。</v>
+        <v>反転 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip ラウンドトリップ 2：1 回目と 2 回目のラウンドトリップの間の ΔE*ab — 繰り返す PCS ラウンドトリップの安定性（再現性。1 回目の色域クリッピングとは無関係）を示します。</v>
+        <v>再現性 (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内の PCS 色を 1 回ラウンドトリップ（Lab → デバイス → Lab）します。ΔE*ab 分布はプロファイル間の相互運用性を示します。</v>
+        <v>PRMG 相互運用性</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>設定</v>
+        <v>iccviz の概要：デバイス値のグリッドを PCS へ、デバイスへ戻し、再び PCS へと変換し、2 回の PCS 結果の間で ΔE*ab を測定します。色域内の安定性を素早く確認します。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>表示</v>
+        <v>iccRoundTrip ラウンドトリップ 1：各デバイス色の PCS と、Lab → デバイス → Lab を 1 回ラウンドトリップした後の PCS との間の ΔE*ab。反転精度と色域マッピングを反映します。</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>背景</v>
+        <v>iccRoundTrip ラウンドトリップ 2：1 回目と 2 回目のラウンドトリップの間の ΔE*ab — 繰り返す PCS ラウンドトリップの安定性（再現性。1 回目の色域クリッピングとは無関係）を示します。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>言語</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内の PCS 色を 1 回ラウンドトリップ（Lab → デバイス → Lab）します。ΔE*ab 分布はプロファイル間の相互運用性を示します。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>システム</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>ライト</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>ダーク</v>
+        <v>背景</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>システム既定</v>
+        <v>言語</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>数値形式</v>
+        <v>システム</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>16 進数</v>
+        <v>ライト</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>10 進数</v>
+        <v>ダーク</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>ヘルプ</v>
+        <v>システム既定</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>お問い合わせ</v>
+        <v>数値形式</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>ユーザーガイド</v>
+        <v>16 進数</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>ガイドを検索</v>
+        <v>10 進数</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>ユーザーガイドを検索</v>
+        <v>ヘルプ</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>前の一致</v>
+        <v>お問い合わせ</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>次の一致</v>
+        <v>ユーザーガイド</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>ユーザーガイドを閉じる</v>
+        <v>ガイドを検索</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>読み込み中…</v>
+        <v>ユーザーガイドを検索</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>ユーザーガイドを読み込めませんでした。</v>
+        <v>前の一致</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>なし</v>
+        <v>次の一致</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ユーザーガイドを閉じる</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v>のデモ実装に基づく</v>
+        <v>ユーザーガイドを読み込めませんでした。</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>検証中…</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>ICC プロファイルを保存</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● 変更あり — 未保存</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>プロファイル</v>
+        <v>のデモ実装に基づく</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>プロファイルプールを表示</v>
+        <v>検証中…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>折りたたむ</v>
+        <v>ICC プロファイルを保存</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>プロファイルを読み込む</v>
+        <v>● 変更あり — 未保存</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>削除</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>プロファイルプールを表示</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
+        <v>折りたたむ</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>.cube から新規作成</v>
+        <v>プロファイルを読み込む</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>名前で並べ替え</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>.cube から新しいプロファイル</v>
+        <v>または画像 (TIFF/PNG/JPEG) をドロップして埋め込みプロファイルを抽出します — ファイルはお使いのデバイス上に留まります。</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
+        <v>.cube から新規作成</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>.cube ファイルを選択</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>.cube から新しいプロファイル</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>.cube ファイルを選択</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>またはここにドロップするか、下に貼り付けてください</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>キャンセル</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>DeviceLink を作成</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>作成中…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>プロファイル</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>比較</v>
+        <v>DeviceLink を作成</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>リンク</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>スペクトル</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>削除</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>色域比較</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>レンダリングインテント</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>シェル</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>軸の数値</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>不透明度</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>色</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>単色</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>値による</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>色相による</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>回転</v>
+        <v>色</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>ターンテーブル</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>オービット</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>ドラッグ速度</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>ロール</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>ロール速度</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>色域を構築中…</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>色域なし</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>表示/非表示</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 色域シェル</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 色域スライス</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>平面</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>リンク</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>プロファイル名</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>作成</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>作成中…</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>リンクパイプライン</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>完了</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>画像を確認中…</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>画像を変換</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>変換中…</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>削除済み</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>前に移動</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>後に移動</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>上に移動</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>下に移動</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>レンダリングインテント（すべて）</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>この変換のレンダリングインテント</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>チェーン</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>チェーンを解析できませんでした。</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>チェーンを確認中…</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>チェーンが接続していません（{detail}）。</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>画像を処理する前にチェーンを修正してください</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>クリア</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLinkを作成</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>DeviceLink名</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>作成中…</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>画像を処理するにはチェーンを作成してください</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>変換した画像を保存しました。</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>データファイルが大きすぎます。</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>データを変換</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>変換中…</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>優先</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>観測者</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>光源</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>条件</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>重複を{n}件フィルタ</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>中央値</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>平均値</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>パッチ</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>重複{n}件</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>変換結果</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} ・ {n}パッチ</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>名前を付けて保存</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>保存</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>変換を反転</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>反転中…</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>反転</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>最後の段階</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>最初の段階</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>{in}のデータ → {out}を検索</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>ΔEコスト</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>この画像には埋め込みICCプロファイルがあります。</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>抽出してチェーンに追加</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>抽出中…</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>閉じる</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>画像出力オプション</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>エンコーディング</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>元と同じ</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8ビット</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16ビット</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>浮動小数点（32ビット）</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>圧縮</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>なし</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>プレーナー</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>コンポジット</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>セパレート</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>CMM補間</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>四面体</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>線形</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>ICCを埋め込む</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>スペクトルTIFFを組み立て</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>ch</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>組み立てて保存</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>組み立て中…</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>{n}チャンネルを組み立てました。</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>キャンセル</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>または</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>ファイルを選択</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>ヘッダー</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>タグ</v>
+        <v>または</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>検証</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>分析</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>中立軸インキング</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>レンダリングインテント</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% インキ</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* 出力（トーン）</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>極値の測色</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
+        <v>L* 出力（トーン）</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>相対</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>絶対</v>
+        <v>極値の測色</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>白色点</v>
+        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>黒色点</v>
+        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>黒色点でのインキング</v>
+        <v>相対</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>絶対</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
+        <v>白色点</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
+        <v>黒色点</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>ベタとクロマ最大点</v>
+        <v>黒色点でのインキング</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>色相</v>
+        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>ベタ</v>
+        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>C* 最大</v>
+        <v>ベタとクロマ最大点</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>そのインキング</v>
+        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>シャドウ部のインキ使用量</v>
+        <v>ベタ</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
+        <v>C* 最大</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>そのインキング</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>L* 一定の平面</v>
+        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>黒色点補償の起点</v>
+        <v>シャドウ部のインキ使用量</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>経路上の位置</v>
+        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>経路</v>
+        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>シアン</v>
+        <v>L* 一定の平面</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>マゼンタ</v>
+        <v>黒色点補償の起点</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>イエロー</v>
+        <v>経路上の位置</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>レッド</v>
+        <v>経路</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>グリーン</v>
+        <v>シアン</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>ブルー</v>
+        <v>マゼンタ</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>ブラック</v>
+        <v>イエロー</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>知覚的</v>
+        <v>レッド</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>相対比色</v>
+        <v>グリーン</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>彩度</v>
+        <v>ブルー</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>絶対比色</v>
+        <v>ブラック</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>プロファイル統計</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>レンダリングインテント</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>往復 ΔE</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>平均</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>最大</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>分析中…</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>分析</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>プロット</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>生出力</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>カーブ</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>入力カーブ</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>出力カーブ</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>CLUT 画像</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>色域画像</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>色度</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>散布図</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>カーブ表</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>テーブル</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>データ</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>評価</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>読み込み中…</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>入力</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>出力</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>浮動小数点</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>グリッド点</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>正規化</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>人間可読</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>デバイス → PCS</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → デバイス</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>読み込み中…</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>セキュリティ</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>適合性</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>品質</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>レポート</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>不合格</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>件のチェック</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>{lib} 採用</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>通知を受け取る</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>閉じる</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>you@example.com</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>（任意）</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>キャンセル</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>登録</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>閉じる</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>エラー:</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>XML に変換</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>JSON に変換</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>ICC に変換</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>XML に変換中…</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>プロファイル ID</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>タグ名</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>オフセット</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>サイズ</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>パディング</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>型</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>{type} の配列</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>（内容なし）</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>バイト</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>型</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>検証出力なし</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>プロファイルは有効です</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>重大な検証エラー</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>不明な検証ステータス</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>有効</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>警告</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>エラー</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>不明</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>合格</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>不合格</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>コンテキストで表示</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>検証の詳細</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>トリガー項目</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>項目</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>現在の値</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>必須: 0</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>期待値: {value}</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>無効</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>閉じる</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>インデント</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>キーをソート</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>シアン</v>
+        <v>中性軸を通る一次色インキ経路</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>マゼンタ</v>
+        <v>色域内の3本の経路——シアン→レッド、マゼンタ→グリーン、イエロー→ブルー——それぞれが両端の明度の中点で中性軸を通り、選択した B2A テーブルを通ります。すべてのサンプルが色域内にあるため、シャドウ経路とは異なり、ある色材の急な段差や反転は色域マッピングのアーティファクトではなく CLUT の滑らかさの欠陥を示します。</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>イエロー</v>
+        <v>一次色インキ経路は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>レッド</v>
+        <v>経路上の位置（中点が中性）</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>グリーン</v>
+        <v>このインテントに黒点補償を適用しました。</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>ブルー</v>
+        <v>インキ使用量の統計</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>ブラック</v>
+        <v>プロファイルが各色材をどれだけ使用するかを、合計と全体に対する割合で示します——分版のインキ消費の特徴です。</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>知覚的</v>
+        <v>インキ使用量の統計は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>相対比色</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>彩度</v>
+        <v>平均被覆率</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>絶対比色</v>
+        <v>インキの割合</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>プロファイル統計</v>
+        <v>インキの割合は中性構築の指紋です——各色材が使用インキ総量に占める割合で、サンプル数に依存しません。</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>色域内の点</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>色域内のすべての色に対するインキ使用量には B2A 方向の色域境界が必要ですが、まだ構築されていません——保留中です。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>レンダリングインテント</v>
+        <v>要約する色材データがありません。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>下で B2A（PCS→デバイス）テーブルを選択すると、各色材のグレースケールのインキ被覆画像も表示されます。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>往復 ΔE</v>
+        <v>同じ格子上での各色材のインキ被覆（暗いほどインキが多い）。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>シアン</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>平均</v>
+        <v>マゼンタ</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>イエロー</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>最大</v>
+        <v>レッド</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>分析中…</v>
+        <v>グリーン</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>分析</v>
+        <v>ブルー</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>ブラック</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>プロット</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>生出力</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>カーブ</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>入力カーブ</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>出力カーブ</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>CLUT 画像</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>色域画像</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>色度</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>散布図</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>カーブ表</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>テーブル</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>データ</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>評価</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>読み込み中…</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>入力</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>出力</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>浮動小数点</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>グリッド点</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>正規化</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>人間可読</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>デバイス → PCS</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → デバイス</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>読み込み中…</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>セキュリティ</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>適合性</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>品質</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>レポート</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>不合格</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>件のチェック</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>{lib} 採用</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>通知を受け取る</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>閉じる</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>メールアドレス</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>（任意）</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>キャンセル</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>登録</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>閉じる</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>エラー:</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>XML に変換</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>ICC に変換</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>XML に変換中…</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>ICC に変換中…</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>プロファイル ID</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>タグが見つかりません。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>タグ名</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>オフセット</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>サイズ</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>パディング</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>型</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>{type} の配列</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>（内容なし）</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>バイト</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>検証出力なし</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>プロファイルは有効です</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>重大な検証エラー</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>不明な検証ステータス</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>有効</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>警告</v>
+        <v>型</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>エラー</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>不明</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>合格</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>不合格</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>コンテキストで表示</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>検証の詳細</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>トリガー項目</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>項目</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>現在の値</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>必須: 0</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>期待値: {value}</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>無効</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>閉じる</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>インデント</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>キーをソート</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>